--- a/Studies/co_analysis/equipment_width_and_crop_profit_factor.xlsx
+++ b/Studies/co_analysis/equipment_width_and_crop_profit_factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmirletz\source\repos\agrivoltaics\co_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmirletz\source\repos\InSPIRE\Studies\co_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EC454E-7DC2-4CBE-9717-8834357931D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FD0EAE-0B6E-4E91-8B74-F74915B943F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{B3449877-09EE-F44E-B1DB-169DB6B5D538}"/>
+    <workbookView xWindow="33135" yWindow="1440" windowWidth="21600" windowHeight="11235" xr2:uid="{B3449877-09EE-F44E-B1DB-169DB6B5D538}"/>
   </bookViews>
   <sheets>
     <sheet name="incremental_row_spacing_calcs" sheetId="20" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="149">
   <si>
     <t>Assumptions</t>
   </si>
@@ -434,6 +434,57 @@
   <si>
     <t>Equipment Agnostic - profit</t>
   </si>
+  <si>
+    <t>Equipment Defined Yield Reduction</t>
+  </si>
+  <si>
+    <t>Orig - Onions - profit</t>
+  </si>
+  <si>
+    <t>Orig - Potatoes - profit</t>
+  </si>
+  <si>
+    <t>Orig - Sugar Beets - profit</t>
+  </si>
+  <si>
+    <t>Orig - Wheat - profit</t>
+  </si>
+  <si>
+    <t>Orig - Equipment Agnostic - profit</t>
+  </si>
+  <si>
+    <t>Orig - Open air - profit</t>
+  </si>
+  <si>
+    <t>Other Farm Sizes</t>
+  </si>
+  <si>
+    <t>Length of a side</t>
+  </si>
+  <si>
+    <t># PV rows total</t>
+  </si>
+  <si>
+    <t>PV power, utility scale</t>
+  </si>
+  <si>
+    <t>PV power, 31.7 ft spacing</t>
+  </si>
+  <si>
+    <t># rows utility scale</t>
+  </si>
+  <si>
+    <t>Total rows of crops</t>
+  </si>
+  <si>
+    <t>Open Field Rows</t>
+  </si>
+  <si>
+    <t>Yield Adjustment</t>
+  </si>
+  <si>
+    <t>At 322/acre</t>
+  </si>
 </sst>
 </file>
 
@@ -600,7 +651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -664,6 +715,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2188,14 +2240,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F5D015-68A1-4B1D-A7AC-25629910F727}">
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.8984375" customWidth="1"/>
     <col min="11" max="12" width="18.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2214,8 +2266,11 @@
       <c r="Y1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2271,25 +2326,43 @@
         <v>121</v>
       </c>
       <c r="Y2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE2" t="s">
         <v>122</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AF2" t="s">
         <v>123</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AG2" t="s">
         <v>124</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AH2" t="s">
         <v>125</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AI2" t="s">
         <v>131</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AJ2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2390,8 +2463,32 @@
       <c r="AD3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE3">
+        <f>1-Y3</f>
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" ref="AF3:AJ15" si="11">1-Z3</f>
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="11"/>
+        <v>0.68862275449101795</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2399,30 +2496,30 @@
         <v>160</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D15" si="11">E4/3.28</f>
+        <f t="shared" ref="D4:D15" si="12">E4/3.28</f>
         <v>6.6158536585365857</v>
       </c>
       <c r="E4">
         <v>21.7</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G15" si="12">B$5/E4</f>
+        <f t="shared" ref="G4:G15" si="13">B$5/E4</f>
         <v>9.6175115207373274</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H15" si="13">_xlfn.FLOOR.MATH(B$3/E4)</f>
+        <f t="shared" ref="H4:H15" si="14">_xlfn.FLOOR.MATH(B$3/E4)</f>
         <v>121</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:K15" si="14">J$3*G4/G$3</f>
+        <f t="shared" ref="J4:K15" si="15">J$3*G4/G$3</f>
         <v>26.087635710380376</v>
       </c>
       <c r="K4">
-        <f t="shared" si="14"/>
+        <f>K$3*H4/H$3</f>
         <v>25.960094400343269</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L4:L15" si="15">K4*$B$10*1000</f>
+        <f t="shared" ref="L4:L15" si="16">K4*$B$10*1000</f>
         <v>34786.526496459985</v>
       </c>
       <c r="N4">
@@ -2450,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <f t="shared" ref="U4:U15" si="16">Q4*$H4</f>
+        <f t="shared" ref="U4:U15" si="17">Q4*$H4</f>
         <v>0</v>
       </c>
       <c r="V4">
@@ -2482,14 +2579,38 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" ref="AC4:AC15" si="17">1-($B$15/E4)</f>
+        <f t="shared" ref="AC4:AC15" si="18">1-($B$15/E4)</f>
         <v>0.47004608294930872</v>
       </c>
       <c r="AD4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE4">
+        <f t="shared" ref="AE4:AE15" si="19">1-Y4</f>
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="11"/>
+        <v>0.52995391705069128</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2497,30 +2618,30 @@
         <v>208.7</v>
       </c>
       <c r="D5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.1402439024390247</v>
       </c>
       <c r="E5">
         <v>26.7</v>
       </c>
       <c r="G5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.8164794007490634</v>
       </c>
       <c r="H5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="J5">
-        <f t="shared" si="14"/>
+        <f>J$3*G5/G$3</f>
         <v>21.202310670983302</v>
       </c>
       <c r="K5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>21.025531001930911</v>
       </c>
       <c r="L5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28174.211542587422</v>
       </c>
       <c r="N5">
@@ -2548,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V5">
@@ -2580,39 +2701,63 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.56928838951310867</v>
       </c>
       <c r="AD5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE5">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="11"/>
+        <v>0.43071161048689133</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="D6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>9.6646341463414629</v>
       </c>
       <c r="E6">
         <v>31.7</v>
       </c>
       <c r="G6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.5835962145110409</v>
       </c>
       <c r="H6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>83</v>
       </c>
       <c r="J6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.858097631396031</v>
       </c>
       <c r="K6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.807337481227201</v>
       </c>
       <c r="L6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23861.832224844453</v>
       </c>
       <c r="N6">
@@ -2640,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>83</v>
       </c>
       <c r="V6">
@@ -2672,14 +2817,38 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.63722397476340698</v>
       </c>
       <c r="AD6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE6">
+        <f t="shared" si="19"/>
+        <v>0.37121212121212122</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="11"/>
+        <v>0.43150684931506844</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="11"/>
+        <v>0.36277602523659302</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -2687,30 +2856,30 @@
         <v>5.9</v>
       </c>
       <c r="D7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11.189024390243905</v>
       </c>
       <c r="E7">
         <v>36.700000000000003</v>
       </c>
       <c r="G7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.6866485013623969</v>
       </c>
       <c r="H7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>71</v>
       </c>
       <c r="J7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.425114302867957</v>
       </c>
       <c r="K7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.232782664664233</v>
       </c>
       <c r="L7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20411.928770650076</v>
       </c>
       <c r="N7">
@@ -2738,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>71</v>
       </c>
       <c r="V7">
@@ -2770,14 +2939,38 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.68664850136239786</v>
       </c>
       <c r="AD7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE7">
+        <f t="shared" si="19"/>
+        <v>0.46212121212121215</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="11"/>
+        <v>0.51369863013698636</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="11"/>
+        <v>0.31335149863760214</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -2786,30 +2979,30 @@
         <v>1.25</v>
       </c>
       <c r="D8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12.713414634146343</v>
       </c>
       <c r="E8">
         <v>41.7</v>
       </c>
       <c r="G8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.0047961630695434</v>
       </c>
       <c r="H8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>63</v>
       </c>
       <c r="J8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.57558021379506</v>
       </c>
       <c r="K8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.516412786955586</v>
       </c>
       <c r="L8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18111.993134520486</v>
       </c>
       <c r="N8">
@@ -2837,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>63</v>
       </c>
       <c r="V8">
@@ -2869,14 +3062,38 @@
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.72422062350119898</v>
       </c>
       <c r="AD8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE8">
+        <f t="shared" si="19"/>
+        <v>0.52272727272727271</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="11"/>
+        <v>0.56849315068493156</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="11"/>
+        <v>0.28409090909090906</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="11"/>
+        <v>0.27577937649880102</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -2885,30 +3102,30 @@
         <v>4.7200000000000006</v>
       </c>
       <c r="D9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14.237804878048783</v>
       </c>
       <c r="E9">
         <v>46.7</v>
       </c>
       <c r="G9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.4689507494646676</v>
       </c>
       <c r="H9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>56</v>
       </c>
       <c r="J9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.122091968206725</v>
       </c>
       <c r="K9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.014589143960523</v>
       </c>
       <c r="L9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>16099.549452907102</v>
       </c>
       <c r="N9">
@@ -2936,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>56</v>
       </c>
       <c r="V9">
@@ -2968,14 +3185,38 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.75374732334047112</v>
       </c>
       <c r="AD9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE9">
+        <f t="shared" si="19"/>
+        <v>0.57575757575757569</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="11"/>
+        <v>0.61643835616438358</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="11"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="11"/>
+        <v>0.24625267665952888</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -2983,30 +3224,30 @@
         <v>1.34</v>
       </c>
       <c r="D10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.762195121951221</v>
       </c>
       <c r="E10">
         <v>51.7</v>
       </c>
       <c r="G10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.0367504835589934</v>
       </c>
       <c r="H10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>51</v>
       </c>
       <c r="J10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.949742648264102</v>
       </c>
       <c r="K10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.941857970392618</v>
       </c>
       <c r="L10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14662.089680326109</v>
       </c>
       <c r="N10">
@@ -3034,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>102</v>
       </c>
       <c r="V10">
@@ -3066,14 +3307,38 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.77756286266924568</v>
       </c>
       <c r="AD10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE10">
+        <f t="shared" si="19"/>
+        <v>0.22727272727272729</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="11"/>
+        <v>0.30136986301369861</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="11"/>
+        <v>0.42045454545454541</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="11"/>
+        <v>0.22243713733075432</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>130</v>
       </c>
@@ -3082,30 +3347,30 @@
         <v>3.5223880597014929</v>
       </c>
       <c r="D11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>17.286585365853661</v>
       </c>
       <c r="E11">
         <v>56.7</v>
       </c>
       <c r="G11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.6807760141093468</v>
       </c>
       <c r="H11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>46</v>
       </c>
       <c r="J11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.9841568768122411</v>
       </c>
       <c r="K11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.8691267968247143</v>
       </c>
       <c r="L11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13224.629907745119</v>
       </c>
       <c r="N11">
@@ -3133,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>92</v>
       </c>
       <c r="V11">
@@ -3165,14 +3430,38 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.7971781305114638</v>
       </c>
       <c r="AD11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE11">
+        <f t="shared" si="19"/>
+        <v>0.30303030303030298</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="11"/>
+        <v>0.36986301369863017</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="11"/>
+        <v>0.47727272727272729</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="11"/>
+        <v>0.2028218694885362</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -3180,30 +3469,30 @@
         <v>7.5</v>
       </c>
       <c r="D12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>18.810975609756099</v>
       </c>
       <c r="E12">
         <v>61.7</v>
       </c>
       <c r="G12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.3824959481361421</v>
       </c>
       <c r="H12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="J12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.1750679889020113</v>
       </c>
       <c r="K12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.0109418579703924</v>
       </c>
       <c r="L12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12074.662089680327</v>
       </c>
       <c r="N12">
@@ -3231,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="U12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="V12">
@@ -3263,42 +3552,66 @@
         <v>0.80769230769230771</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.81361426256077796</v>
       </c>
       <c r="AD12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE12">
+        <f t="shared" si="19"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="11"/>
+        <v>0.42465753424657537</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="11"/>
+        <v>0.52272727272727271</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="11"/>
+        <v>0.19230769230769229</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="11"/>
+        <v>0.18638573743922204</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="D13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>20.335365853658537</v>
       </c>
       <c r="E13">
         <v>66.7</v>
       </c>
       <c r="G13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.1289355322338825</v>
       </c>
       <c r="H13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>39</v>
       </c>
       <c r="J13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.4872817828373925</v>
       </c>
       <c r="K13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.3673031538296492</v>
       </c>
       <c r="L13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11212.186226131731</v>
       </c>
       <c r="N13">
@@ -3326,7 +3639,7 @@
         <v>1</v>
       </c>
       <c r="U13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>78</v>
       </c>
       <c r="V13">
@@ -3358,14 +3671,38 @@
         <v>0.75</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.82758620689655171</v>
       </c>
       <c r="AD13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE13">
+        <f t="shared" si="19"/>
+        <v>0.40909090909090906</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="11"/>
+        <v>0.19863013698630139</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="11"/>
+        <v>0.55681818181818188</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="11"/>
+        <v>0.25</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="11"/>
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -3373,30 +3710,30 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21.859756097560979</v>
       </c>
       <c r="E14">
         <v>71.7</v>
       </c>
       <c r="G14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.9107391910739189</v>
       </c>
       <c r="H14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="J14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.8954211285251619</v>
       </c>
       <c r="K14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.7236644496889069</v>
       </c>
       <c r="L14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10349.710362583135</v>
       </c>
       <c r="N14">
@@ -3424,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="U14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>108</v>
       </c>
       <c r="V14">
@@ -3456,14 +3793,38 @@
         <v>0.69230769230769229</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.83960948396094837</v>
       </c>
       <c r="AD14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE14">
+        <f t="shared" si="19"/>
+        <v>0.18181818181818177</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="11"/>
+        <v>0.26027397260273977</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="11"/>
+        <v>0.18181818181818177</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="11"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="11"/>
+        <v>0.16039051603905163</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -3472,30 +3833,30 @@
         <v>11.5</v>
       </c>
       <c r="D15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>23.384146341463417</v>
       </c>
       <c r="E15">
         <v>76.7</v>
       </c>
       <c r="G15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.7209908735332462</v>
       </c>
       <c r="H15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>34</v>
       </c>
       <c r="J15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.3807261397034427</v>
       </c>
       <c r="K15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.294571980261745</v>
       </c>
       <c r="L15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9774.7264535507402</v>
       </c>
       <c r="N15">
@@ -3523,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="U15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>102</v>
       </c>
       <c r="V15">
@@ -3555,56 +3916,348 @@
         <v>0.65384615384615385</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.85006518904823991</v>
       </c>
       <c r="AD15">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="AE15">
+        <f t="shared" si="19"/>
+        <v>0.22727272727272729</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="11"/>
+        <v>0.30136986301369861</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="11"/>
+        <v>0.22727272727272729</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="11"/>
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="11"/>
+        <v>0.14993481095176009</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
       <c r="B18">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" t="s">
+        <v>143</v>
+      </c>
+      <c r="K18" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" t="s">
+        <v>145</v>
+      </c>
+      <c r="M18" t="s">
+        <v>146</v>
+      </c>
+      <c r="N18" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" t="s">
+        <v>147</v>
+      </c>
+      <c r="P18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>80</v>
+      </c>
+      <c r="F19" s="33">
+        <v>1867</v>
+      </c>
+      <c r="G19">
+        <f>_xlfn.FLOOR.MATH(F19/16.7)</f>
+        <v>111</v>
+      </c>
+      <c r="H19">
+        <f>_xlfn.FLOOR.MATH(F19/$E$6)</f>
+        <v>58</v>
+      </c>
+      <c r="I19">
+        <f>E19/$B$7</f>
+        <v>13.559322033898304</v>
+      </c>
+      <c r="J19">
+        <f>I19*H19/G19</f>
+        <v>7.0850511528477629</v>
+      </c>
+      <c r="K19">
+        <f>J19*$B$10*1000</f>
+        <v>9493.9685448160035</v>
+      </c>
+      <c r="L19">
+        <f>H19</f>
+        <v>58</v>
+      </c>
+      <c r="M19">
+        <f>_xlfn.FLOOR.MATH(F19/$B$18)</f>
+        <v>93</v>
+      </c>
+      <c r="N19">
+        <f>L19/M19</f>
+        <v>0.62365591397849462</v>
+      </c>
+      <c r="O19">
+        <f>1-N19</f>
+        <v>0.37634408602150538</v>
+      </c>
+      <c r="P19">
+        <f>322*E19*N19</f>
+        <v>16065.376344086022</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E20">
+        <v>120</v>
+      </c>
+      <c r="F20">
+        <v>2286.3000000000002</v>
+      </c>
+      <c r="G20">
+        <f>_xlfn.FLOOR.MATH(F20/16.7)</f>
+        <v>136</v>
+      </c>
+      <c r="H20">
+        <f>_xlfn.FLOOR.MATH(F20/$E$6)</f>
+        <v>72</v>
+      </c>
+      <c r="I20">
+        <f>E20/$B$7</f>
+        <v>20.338983050847457</v>
+      </c>
+      <c r="J20">
+        <f>I20*H20/G20</f>
+        <v>10.767696909272182</v>
+      </c>
+      <c r="K20">
+        <f>J20*$B$10*1000</f>
+        <v>14428.713858424726</v>
+      </c>
+      <c r="L20">
+        <f>H20</f>
+        <v>72</v>
+      </c>
+      <c r="M20">
+        <f>_xlfn.FLOOR.MATH(F20/$B$18)</f>
+        <v>114</v>
+      </c>
+      <c r="N20">
+        <f t="shared" ref="N20:N22" si="20">L20/M20</f>
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="O20">
+        <f>1-N20</f>
+        <v>0.36842105263157898</v>
+      </c>
+      <c r="P20">
+        <f>322*E20*N20</f>
+        <v>24404.210526315786</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
       <c r="B21">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E21">
+        <v>160</v>
+      </c>
+      <c r="F21">
+        <v>2640</v>
+      </c>
+      <c r="G21">
+        <f>_xlfn.FLOOR.MATH(F21/16.7)</f>
+        <v>158</v>
+      </c>
+      <c r="H21">
+        <f>_xlfn.FLOOR.MATH(F21/$E$6)</f>
+        <v>83</v>
+      </c>
+      <c r="I21">
+        <f>E21/$B$7</f>
+        <v>27.118644067796609</v>
+      </c>
+      <c r="J21">
+        <f>I21*H21/G21</f>
+        <v>14.245869984981764</v>
+      </c>
+      <c r="K21">
+        <f>J21*$B$10*1000</f>
+        <v>19089.465779875565</v>
+      </c>
+      <c r="L21">
+        <f>H21</f>
+        <v>83</v>
+      </c>
+      <c r="M21">
+        <f>_xlfn.FLOOR.MATH(F21/$B$18)</f>
+        <v>132</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="20"/>
+        <v>0.62878787878787878</v>
+      </c>
+      <c r="O21">
+        <f>1-N21</f>
+        <v>0.37121212121212122</v>
+      </c>
+      <c r="P21">
+        <f>322*E21*N21</f>
+        <v>32395.151515151516</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>320</v>
+      </c>
+      <c r="F22">
+        <v>3733.5</v>
+      </c>
+      <c r="G22">
+        <f>_xlfn.FLOOR.MATH(F22/16.7)</f>
+        <v>223</v>
+      </c>
+      <c r="H22">
+        <f>_xlfn.FLOOR.MATH(F22/$E$6)</f>
+        <v>117</v>
+      </c>
+      <c r="I22">
+        <f>E22/$B$7</f>
+        <v>54.237288135593218</v>
+      </c>
+      <c r="J22">
+        <f>I22*H22/G22</f>
+        <v>28.456335030782093</v>
+      </c>
+      <c r="K22">
+        <f>J22*$B$10*1000</f>
+        <v>38131.488941248012</v>
+      </c>
+      <c r="L22">
+        <f>H22</f>
+        <v>117</v>
+      </c>
+      <c r="M22">
+        <f>_xlfn.FLOOR.MATH(F22/$B$18)</f>
+        <v>186</v>
+      </c>
+      <c r="N22">
+        <f t="shared" ref="N22:N23" si="21">L22/M22</f>
+        <v>0.62903225806451613</v>
+      </c>
+      <c r="O22">
+        <f>1-N22</f>
+        <v>0.37096774193548387</v>
+      </c>
+      <c r="P22">
+        <f>322*E22*N22</f>
+        <v>64815.483870967742</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E23">
+        <v>640</v>
+      </c>
+      <c r="F23">
+        <v>5280</v>
+      </c>
+      <c r="G23">
+        <f>_xlfn.FLOOR.MATH(F23/16.7)</f>
+        <v>316</v>
+      </c>
+      <c r="H23">
+        <f>_xlfn.FLOOR.MATH(F23/$E$6)</f>
+        <v>166</v>
+      </c>
+      <c r="I23">
+        <f>E23/$B$7</f>
+        <v>108.47457627118644</v>
+      </c>
+      <c r="J23">
+        <f>I23*H23/G23</f>
+        <v>56.983479939927058</v>
+      </c>
+      <c r="K23">
+        <f>J23*$B$10*1000</f>
+        <v>76357.863119502261</v>
+      </c>
+      <c r="L23">
+        <f>H23</f>
+        <v>166</v>
+      </c>
+      <c r="M23">
+        <f>_xlfn.FLOOR.MATH(F23/$B$18)</f>
+        <v>264</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="21"/>
+        <v>0.62878787878787878</v>
+      </c>
+      <c r="O23">
+        <f>1-N23</f>
+        <v>0.37121212121212122</v>
+      </c>
+      <c r="P23">
+        <f>322*E23*N23</f>
+        <v>129580.60606060606</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3613,7 +4266,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -3622,7 +4275,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -3631,7 +4284,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -3640,7 +4293,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>128</v>
       </c>
@@ -3648,7 +4301,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>42.9/247.105</f>
         <v>0.17361040853078652</v>
@@ -3658,7 +4311,7 @@
         <v>4.29852485822635</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>1/A30</f>
         <v>5.7600233100233096</v>
